--- a/outputs/strategy_order_tracker/monthly_rotation_order_tracker.xlsx
+++ b/outputs/strategy_order_tracker/monthly_rotation_order_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/khand/Git/pmcc_backtest_ruby/outputs/strategy_order_tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1941E75D-1DF4-254A-97C9-127F467B16F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF5A4C3-1C40-3846-AF39-DDD494656EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18900" yWindow="11620" windowWidth="41000" windowHeight="18700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20340" yWindow="3640" windowWidth="41000" windowHeight="18700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -248,9 +248,6 @@
     <t>Limit</t>
   </si>
   <si>
-    <t>Initial tracker entry; filled in extended hours</t>
-  </si>
-  <si>
     <t>Sell</t>
   </si>
   <si>
@@ -258,9 +255,6 @@
   </si>
   <si>
     <t>Working</t>
-  </si>
-  <si>
-    <t>GTC protective stop at 90% of $69.70 reference</t>
   </si>
   <si>
     <t>How to Use This Tracker</t>
@@ -336,6 +330,12 @@
   </si>
   <si>
     <t>Risk note: stop-market orders do not guarantee execution at the stop price. Leveraged ETFs can gap through the stop, and the historical strategy experienced drawdowns exceeding 50%.</t>
+  </si>
+  <si>
+    <t>GTC protective stop at 90% of $70.36 reference</t>
+  </si>
+  <si>
+    <t>Initial tracker entry</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B7" s="12">
         <f>SUMIFS(Orders!$G$7:$G$506,Orders!$E$7:$E$506,B6,Orders!$H$7:$H$506,"Filled")</f>
-        <v>9</v>
+        <v>364</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B8" s="13">
         <f>IF(COUNTIFS(Orders!$E$7:$E$506,B6,Orders!$D$7:$D$506,"Buy",Orders!$H$7:$H$506,"Filled",Orders!$B$7:$B$506,MAX('Monthly Signals'!$A$7:$A$126))=0,"",SUMIFS(Orders!$K$7:$K$506,Orders!$E$7:$E$506,B6,Orders!$D$7:$D$506,"Buy",Orders!$H$7:$H$506,"Filled",Orders!$B$7:$B$506,MAX('Monthly Signals'!$A$7:$A$126))/COUNTIFS(Orders!$E$7:$E$506,B6,Orders!$D$7:$D$506,"Buy",Orders!$H$7:$H$506,"Filled",Orders!$B$7:$B$506,MAX('Monthly Signals'!$A$7:$A$126)))</f>
-        <v>69.7</v>
+        <v>70.363200000000006</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B9" s="13">
         <f>IF(COUNTIFS(Orders!$E$7:$E$506,B6,Orders!$F$7:$F$506,"Stop",Orders!$H$7:$H$506,"Working")=0,"",SUMIFS(Orders!$J$7:$J$506,Orders!$E$7:$E$506,B6,Orders!$F$7:$F$506,"Stop",Orders!$H$7:$H$506,"Working"))</f>
-        <v>62.73</v>
+        <v>63.32</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6" t="s">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B10" s="14">
         <f>IF(OR(B8="",B9=""),"",B9/B8-1)</f>
-        <v>-0.10000000000000009</v>
+        <v>-0.10009777838415546</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9" t="s">
@@ -1723,54 +1723,54 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="23">
+        <v>46268.451388888891</v>
+      </c>
+      <c r="B7" s="24">
         <v>46267.5</v>
       </c>
-      <c r="B7" s="24">
-        <v>46266.5</v>
-      </c>
       <c r="C7" s="25">
-        <v>707.64</v>
+        <v>709.24</v>
       </c>
       <c r="D7" s="25">
-        <v>654.74</v>
+        <v>655.30999999999995</v>
       </c>
       <c r="E7" s="26">
-        <v>1.7390000000000001E-3</v>
+        <v>1.6050000000000001E-3</v>
       </c>
       <c r="F7" s="27" t="str">
         <f t="shared" ref="F7:F38" si="0">IF(OR(C7="",D7="",E7=""),"",IF(AND(C7&gt;D7,E7&gt;0),"Risk-on","Defensive"))</f>
         <v>Risk-on</v>
       </c>
       <c r="G7" s="26">
-        <v>-0.12620000000000001</v>
+        <v>-0.14169999999999999</v>
       </c>
       <c r="H7" s="26">
-        <v>-0.19900000000000001</v>
+        <v>-0.18279999999999999</v>
       </c>
       <c r="I7" s="26">
-        <v>-8.8999999999999996E-2</v>
+        <v>-5.5599999999999997E-2</v>
       </c>
       <c r="J7" s="26">
-        <v>-7.9000000000000008E-3</v>
+        <v>-8.5000000000000006E-3</v>
       </c>
       <c r="K7" s="26">
-        <v>-1.1999999999999999E-3</v>
+        <v>-1.6000000000000001E-3</v>
       </c>
       <c r="L7" s="28" t="s">
         <v>53</v>
       </c>
       <c r="M7" s="29">
-        <v>664.26</v>
+        <v>25900</v>
       </c>
       <c r="N7" s="30">
         <v>0.99</v>
       </c>
       <c r="O7" s="25">
-        <v>69.7</v>
+        <v>70.363200000000006</v>
       </c>
       <c r="P7" s="28">
         <f t="shared" ref="P7:P38" si="1">IF(OR(M7="",N7="",O7=""),"",ROUNDDOWN(M7*N7/O7,0))</f>
-        <v>9</v>
+        <v>364</v>
       </c>
       <c r="Q7" s="31" t="str">
         <f t="shared" ref="Q7:Q38" si="2">IF(A7="","",IF(COUNT(C7:E7)+COUNT(G7:K7)=8,"OK","CHECK"))</f>
@@ -5695,13 +5695,13 @@
     </row>
     <row r="7" spans="1:15" ht="15">
       <c r="A7" s="23">
+        <v>46268.451388888891</v>
+      </c>
+      <c r="B7" s="23">
+        <v>46268.451388888891</v>
+      </c>
+      <c r="C7" s="24">
         <v>46267.5</v>
-      </c>
-      <c r="B7" s="24">
-        <v>46267.5</v>
-      </c>
-      <c r="C7" s="24">
-        <v>46266.5</v>
       </c>
       <c r="D7" s="41" t="s">
         <v>68</v>
@@ -5713,57 +5713,57 @@
         <v>69</v>
       </c>
       <c r="G7" s="41">
-        <v>9</v>
+        <v>364</v>
       </c>
       <c r="H7" s="41" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="25">
-        <v>69.7</v>
+        <v>70.363200000000006</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="25">
-        <v>69.7</v>
+        <v>70.363200000000006</v>
       </c>
       <c r="L7" s="24">
-        <v>46267.5</v>
+        <v>46268.451388888891</v>
       </c>
       <c r="M7" s="42">
         <v>0</v>
       </c>
       <c r="N7" s="42"/>
       <c r="O7" s="45" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15">
       <c r="A8" s="23">
+        <v>46268.45208333333</v>
+      </c>
+      <c r="B8" s="23">
+        <v>46268.45208333333</v>
+      </c>
+      <c r="C8" s="24">
         <v>46267.5</v>
       </c>
-      <c r="B8" s="24">
-        <v>46267.5</v>
-      </c>
-      <c r="C8" s="24">
-        <v>46266.5</v>
-      </c>
       <c r="D8" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="41" t="s">
         <v>53</v>
       </c>
       <c r="F8" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="41">
+        <v>-364</v>
+      </c>
+      <c r="H8" s="41" t="s">
         <v>72</v>
-      </c>
-      <c r="G8" s="41">
-        <v>-9</v>
-      </c>
-      <c r="H8" s="41" t="s">
-        <v>73</v>
       </c>
       <c r="I8" s="25"/>
       <c r="J8" s="25">
-        <v>62.73</v>
+        <v>63.32</v>
       </c>
       <c r="K8" s="25"/>
       <c r="L8" s="24"/>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="N8" s="42"/>
       <c r="O8" s="45" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -14285,62 +14285,62 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E1" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F1" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="34" customHeight="1">
       <c r="A2" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F2" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="23" customHeight="1">
       <c r="A4" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B4" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D4" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="31">
@@ -14348,10 +14348,10 @@
         <v>22</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -14359,10 +14359,10 @@
         <v>24</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="31">
@@ -14370,10 +14370,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="31">
@@ -14381,10 +14381,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -14392,10 +14392,10 @@
         <v>30</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" s="53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -14403,103 +14403,103 @@
         <v>32</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="23" customHeight="1">
       <c r="A12" s="61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12" s="61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E12" s="61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F12" s="61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B17" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D17" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E17" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B18" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D18" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E18" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
